--- a/artfynd/A 29339-2026 artfynd.xlsx
+++ b/artfynd/A 29339-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,53 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135261503</v>
+        <v>135282281</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skinnarbodstjärn, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455453</v>
+        <v>455475</v>
       </c>
       <c r="R5" t="n">
-        <v>6786195</v>
+        <v>6786212</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,64 +1087,89 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135261507</v>
+        <v>135261503</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skinnarbodstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455479</v>
+        <v>455453</v>
       </c>
       <c r="R6" t="n">
-        <v>6786209</v>
+        <v>6786195</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135261510</v>
+        <v>135261507</v>
       </c>
       <c r="B7" t="n">
         <v>79405</v>
@@ -1250,13 +1270,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455502</v>
+        <v>455479</v>
       </c>
       <c r="R7" t="n">
-        <v>6786211</v>
+        <v>6786209</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135261513</v>
+        <v>135261510</v>
       </c>
       <c r="B8" t="n">
         <v>79405</v>
@@ -1357,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455551</v>
+        <v>455502</v>
       </c>
       <c r="R8" t="n">
-        <v>6786233</v>
+        <v>6786211</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135261516</v>
+        <v>135261513</v>
       </c>
       <c r="B9" t="n">
         <v>79405</v>
@@ -1464,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455479</v>
+        <v>455551</v>
       </c>
       <c r="R9" t="n">
-        <v>6786182</v>
+        <v>6786233</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1556,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135261505</v>
+        <v>135261516</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1594,10 @@
         <v>455479</v>
       </c>
       <c r="R10" t="n">
-        <v>6786205</v>
+        <v>6786182</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,48 +1663,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135261506</v>
+        <v>135282282</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skinnarbodstjärn, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455479</v>
+        <v>455494</v>
       </c>
       <c r="R11" t="n">
-        <v>6786209</v>
+        <v>6786206</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,23 +1754,43 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135261509</v>
+        <v>135261505</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1785,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455487</v>
+        <v>455479</v>
       </c>
       <c r="R12" t="n">
         <v>6786205</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,7 +1897,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135261511</v>
+        <v>135261506</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1892,13 +1932,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455503</v>
+        <v>455479</v>
       </c>
       <c r="R13" t="n">
-        <v>6786216</v>
+        <v>6786209</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135261512</v>
+        <v>135261509</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -1999,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455521</v>
+        <v>455487</v>
       </c>
       <c r="R14" t="n">
-        <v>6786230</v>
+        <v>6786205</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2034,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135261514</v>
+        <v>135261511</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2100,22 +2140,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnarbodstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455532</v>
+        <v>455503</v>
       </c>
       <c r="R15" t="n">
-        <v>6786214</v>
+        <v>6786216</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2144,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2154,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2200,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2182,7 +2218,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135261515</v>
+        <v>135261512</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2217,13 +2253,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455493</v>
+        <v>455521</v>
       </c>
       <c r="R16" t="n">
-        <v>6786185</v>
+        <v>6786230</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2252,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,6 +2322,833 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135261514</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skinnarbodstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>455532</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6786214</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135261515</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skinnarbodstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>455493</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6786185</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135282283</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skinnarbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>455500</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6786214</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135282284</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skinnarbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>455548</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6786203</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135282288</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skinnarbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>455489</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6786184</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135282287</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skinnarbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>455513</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6786201</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135282285</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skinnarbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>455516</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6786204</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29339-2026 artfynd.xlsx
+++ b/artfynd/A 29339-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261502</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261504</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261501</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282281</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261503</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261507</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261510</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261513</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261516</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282282</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261505</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261506</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261509</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261511</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261512</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261514</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2540,6 +2625,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261515</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2667,6 +2757,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282283</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2794,6 +2889,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282284</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2921,6 +3021,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282288</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3033,6 +3138,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282287</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3149,8 +3259,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282285</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29339-2026 artfynd.xlsx
+++ b/artfynd/A 29339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135261502</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135261504</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135261501</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135282281</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135261503</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135261507</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135261510</v>
       </c>
       <c r="B8" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>135261513</v>
       </c>
       <c r="B9" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135261516</v>
       </c>
       <c r="B10" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>135282282</v>
       </c>
       <c r="B11" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135261505</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>135261506</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>135261509</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135261511</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>135261512</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>135261514</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>135261515</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135282283</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>135282284</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>135282288</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>135282287</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>135282285</v>
       </c>
       <c r="B23" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29339-2026 artfynd.xlsx
+++ b/artfynd/A 29339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135261502</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135261504</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135261501</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135282281</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135261507</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135261510</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>135261513</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135261516</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>135282282</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135261505</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>135261506</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>135261509</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135261511</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>135261512</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>135261514</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>135261515</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135282283</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>135282284</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>135282288</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>135282285</v>
       </c>
       <c r="B23" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29339-2026 artfynd.xlsx
+++ b/artfynd/A 29339-2026 artfynd.xlsx
@@ -3149,7 +3149,7 @@
         <v>135282285</v>
       </c>
       <c r="B23" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
